--- a/spectakeoff/Batch_Summary.xlsx
+++ b/spectakeoff/Batch_Summary.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -515,14 +515,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RCCD.pdf</t>
+          <t>UM-Barrows-Hall-Chiller-Replacement-Specifications.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>509</v>
+        <v>290</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Service 15, Extended Warranty 14, O&amp;M Deliverable 11, Quantity Not Specified 10, Training 9, Spare Part 9, Attic Stock 5, Special Tool 2</t>
+          <t>Extended Warranty 8, Training 5, Quantity Not Specified 1</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -561,36 +561,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ECISD.pdf</t>
+          <t>UCCS_Cragmor_Hall_Chiller_Replacement_-_Project_Manual_1.pdf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>both (mixed manual)</t>
+          <t>MasterFormat 2004</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Div 15-16 Coverage</t>
+          <t>Div 23-26 Coverage</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -599,10 +599,56 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Quantity Not Specified 13, O&amp;M Deliverable 7, Attic Stock 2, Extended Warranty 2, Maintenance Service 1</t>
+          <t>Quantity Not Specified 16, O&amp;M Deliverable 7, Extended Warranty 7, Training 4, Special Tool 3, Attic Stock 1, Spare Part 1</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>253101-Mechanical-Equipment-Replacement_Specs.pdf</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MasterFormat 2004</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Div 23-26 Coverage</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Extended Warranty 11, Quantity Not Specified 7, O&amp;M Deliverable 6, Spare Part 4, Attic Stock 4, Maintenance Service 1, Training 1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
